--- a/data/Copy of Acute ladder rung test.xlsx
+++ b/data/Copy of Acute ladder rung test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nickhousley/GaTech Dropbox/Nick Housley/papers_dropbox/acute_OX_paper/data/behavior/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nickhousley/GaTech Dropbox/CoS/BioSci/BioSci-Housley_Lab/04-papers/acute_ox/acute_oxaliplatin_encoding/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0832C92-ABC9-864F-B2DE-2C1349A3FEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AEAEFB-8A08-4A49-BCA9-18B63772C9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{B02F0EC0-EBCD-4D84-A4FD-30B77E72A40C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t>treat</t>
   </si>
@@ -72,6 +72,84 @@
   </si>
   <si>
     <t>slips_per_step</t>
+  </si>
+  <si>
+    <t>rat_run</t>
+  </si>
+  <si>
+    <t>1a</t>
+  </si>
+  <si>
+    <t>1b</t>
+  </si>
+  <si>
+    <t>1c</t>
+  </si>
+  <si>
+    <t>1d</t>
+  </si>
+  <si>
+    <t>1e</t>
+  </si>
+  <si>
+    <t>2a</t>
+  </si>
+  <si>
+    <t>2b</t>
+  </si>
+  <si>
+    <t>2c</t>
+  </si>
+  <si>
+    <t>2d</t>
+  </si>
+  <si>
+    <t>2e</t>
+  </si>
+  <si>
+    <t>3a</t>
+  </si>
+  <si>
+    <t>3b</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>3e</t>
+  </si>
+  <si>
+    <t>4a</t>
+  </si>
+  <si>
+    <t>4b</t>
+  </si>
+  <si>
+    <t>4c</t>
+  </si>
+  <si>
+    <t>4d</t>
+  </si>
+  <si>
+    <t>4e</t>
+  </si>
+  <si>
+    <t>5a</t>
+  </si>
+  <si>
+    <t>5b</t>
+  </si>
+  <si>
+    <t>5c</t>
+  </si>
+  <si>
+    <t>5d</t>
+  </si>
+  <si>
+    <t>5e</t>
   </si>
 </sst>
 </file>
@@ -492,6 +570,9 @@
       <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
@@ -524,6 +605,9 @@
       <c r="J2" s="1">
         <v>0.22222222222222221</v>
       </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
       <c r="M2" t="s">
         <v>1</v>
       </c>
@@ -570,6 +654,9 @@
       </c>
       <c r="J3" s="1">
         <v>0.4</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
@@ -622,6 +709,9 @@
       <c r="J4" s="1">
         <v>0.35714285714285715</v>
       </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
       <c r="N4">
         <f>STDEV(J2:J6)</f>
         <v>0.12615353357620093</v>
@@ -670,6 +760,9 @@
       <c r="J5" s="1">
         <v>0.21428571428571427</v>
       </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -702,6 +795,9 @@
       <c r="J6" s="1">
         <v>8.3333333333333329E-2</v>
       </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -734,6 +830,9 @@
       <c r="J7" s="1">
         <v>0.2</v>
       </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -766,6 +865,9 @@
       <c r="J8" s="1">
         <v>0.1111111111111111</v>
       </c>
+      <c r="K8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
@@ -798,6 +900,9 @@
       <c r="J9" s="1">
         <v>0.33333333333333331</v>
       </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -830,6 +935,9 @@
       <c r="J10" s="1">
         <v>0.22222222222222221</v>
       </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -862,6 +970,9 @@
       <c r="J11" s="1">
         <v>0.33333333333333331</v>
       </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -894,6 +1005,9 @@
       <c r="J12" s="1">
         <v>0.61538461538461542</v>
       </c>
+      <c r="K12" t="s">
+        <v>18</v>
+      </c>
       <c r="M12" t="s">
         <v>1</v>
       </c>
@@ -940,6 +1054,9 @@
       </c>
       <c r="J13" s="1">
         <v>0.5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
       </c>
       <c r="M13" s="1">
         <v>2</v>
@@ -992,6 +1109,9 @@
       <c r="J14" s="1">
         <v>0.61538461538461542</v>
       </c>
+      <c r="K14" t="s">
+        <v>20</v>
+      </c>
       <c r="N14">
         <f>STDEV(J12:J16)</f>
         <v>0.14315920394457687</v>
@@ -1040,6 +1160,9 @@
       <c r="J15" s="1">
         <v>0.88888888888888884</v>
       </c>
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -1072,6 +1195,9 @@
       <c r="J16" s="1">
         <v>0.66666666666666663</v>
       </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
@@ -1104,6 +1230,9 @@
       <c r="J17" s="1">
         <v>0.8571428571428571</v>
       </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
@@ -1136,6 +1265,9 @@
       <c r="J18" s="1">
         <v>0.91666666666666663</v>
       </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
@@ -1168,6 +1300,9 @@
       <c r="J19" s="1">
         <v>0.6428571428571429</v>
       </c>
+      <c r="K19" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -1200,6 +1335,9 @@
       <c r="J20" s="1">
         <v>0.69230769230769229</v>
       </c>
+      <c r="K20" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -1232,6 +1370,9 @@
       <c r="J21" s="1">
         <v>0.81818181818181823</v>
       </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
@@ -1264,6 +1405,9 @@
       <c r="J22" s="1">
         <v>0.3</v>
       </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
       <c r="M22" t="s">
         <v>1</v>
       </c>
@@ -1310,6 +1454,9 @@
       </c>
       <c r="J23" s="1">
         <v>0.36363636363636365</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
       </c>
       <c r="M23" s="1">
         <v>3</v>
@@ -1362,6 +1509,9 @@
       <c r="J24" s="1">
         <v>0.3</v>
       </c>
+      <c r="K24" t="s">
+        <v>25</v>
+      </c>
       <c r="N24">
         <f>STDEV(J22:J26)</f>
         <v>9.2181254792641915E-2</v>
@@ -1410,6 +1560,9 @@
       <c r="J25" s="1">
         <v>0.5</v>
       </c>
+      <c r="K25" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -1442,6 +1595,9 @@
       <c r="J26" s="1">
         <v>0.46153846153846156</v>
       </c>
+      <c r="K26" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -1474,6 +1630,9 @@
       <c r="J27" s="1">
         <v>0.41666666666666669</v>
       </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1506,6 +1665,9 @@
       <c r="J28" s="1">
         <v>0.27272727272727271</v>
       </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
@@ -1538,6 +1700,9 @@
       <c r="J29" s="1">
         <v>0.45454545454545453</v>
       </c>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
@@ -1570,6 +1735,9 @@
       <c r="J30" s="1">
         <v>0.4</v>
       </c>
+      <c r="K30" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
@@ -1602,6 +1770,9 @@
       <c r="J31" s="1">
         <v>0.45454545454545453</v>
       </c>
+      <c r="K31" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
@@ -1634,6 +1805,9 @@
       <c r="J32" s="1">
         <v>7.1428571428571425E-2</v>
       </c>
+      <c r="K32" t="s">
+        <v>28</v>
+      </c>
       <c r="M32" t="s">
         <v>1</v>
       </c>
@@ -1680,6 +1854,9 @@
       </c>
       <c r="J33" s="1">
         <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>29</v>
       </c>
       <c r="M33" s="1">
         <v>4</v>
@@ -1732,6 +1909,9 @@
       <c r="J34" s="1">
         <v>0.18181818181818182</v>
       </c>
+      <c r="K34" t="s">
+        <v>30</v>
+      </c>
       <c r="N34">
         <f>STDEV(J32:J36)</f>
         <v>8.2946818259626076E-2</v>
@@ -1780,6 +1960,9 @@
       <c r="J35" s="1">
         <v>8.3333333333333329E-2</v>
       </c>
+      <c r="K35" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
@@ -1812,6 +1995,9 @@
       <c r="J36" s="1">
         <v>0.2</v>
       </c>
+      <c r="K36" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
@@ -1844,6 +2030,9 @@
       <c r="J37" s="1">
         <v>0.3</v>
       </c>
+      <c r="K37" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
@@ -1876,6 +2065,9 @@
       <c r="J38" s="1">
         <v>0.27272727272727271</v>
       </c>
+      <c r="K38" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
@@ -1908,6 +2100,9 @@
       <c r="J39" s="1">
         <v>0.2</v>
       </c>
+      <c r="K39" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
@@ -1940,6 +2135,9 @@
       <c r="J40" s="1">
         <v>0.25</v>
       </c>
+      <c r="K40" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
@@ -1972,6 +2170,9 @@
       <c r="J41" s="1">
         <v>9.0909090909090912E-2</v>
       </c>
+      <c r="K41" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
@@ -2004,6 +2205,9 @@
       <c r="J42" s="1">
         <v>0.18181818181818182</v>
       </c>
+      <c r="K42" t="s">
+        <v>33</v>
+      </c>
       <c r="M42" t="s">
         <v>1</v>
       </c>
@@ -2050,6 +2254,9 @@
       </c>
       <c r="J43" s="1">
         <v>0.36363636363636365</v>
+      </c>
+      <c r="K43" t="s">
+        <v>34</v>
       </c>
       <c r="M43" s="1">
         <v>5</v>
@@ -2102,6 +2309,9 @@
       <c r="J44" s="1">
         <v>9.0909090909090912E-2</v>
       </c>
+      <c r="K44" t="s">
+        <v>35</v>
+      </c>
       <c r="N44">
         <f>STDEV(J42:J46)</f>
         <v>0.16693642081655319</v>
@@ -2150,6 +2360,9 @@
       <c r="J45" s="1">
         <v>0.4</v>
       </c>
+      <c r="K45" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
@@ -2182,6 +2395,9 @@
       <c r="J46" s="1">
         <v>0.5</v>
       </c>
+      <c r="K46" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
@@ -2214,6 +2430,9 @@
       <c r="J47" s="1">
         <v>0.36363636363636365</v>
       </c>
+      <c r="K47" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
@@ -2246,8 +2465,11 @@
       <c r="J48" s="1">
         <v>0.2857142857142857</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2278,8 +2500,11 @@
       <c r="J49" s="1">
         <v>0.18181818181818182</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -2310,8 +2535,11 @@
       <c r="J50" s="1">
         <v>0.44444444444444442</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -2341,6 +2569,9 @@
       </c>
       <c r="J51" s="1">
         <v>0.30769230769230771</v>
+      </c>
+      <c r="K51" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/Copy of Acute ladder rung test.xlsx
+++ b/data/Copy of Acute ladder rung test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nickhousley/GaTech Dropbox/CoS/BioSci/BioSci-Housley_Lab/04-papers/acute_ox/acute_oxaliplatin_encoding/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3AEAEFB-8A08-4A49-BCA9-18B63772C9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D8A28A-DE2B-DB4B-A141-118B42756926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{B02F0EC0-EBCD-4D84-A4FD-30B77E72A40C}"/>
   </bookViews>
